--- a/shabbatot/2026-10-30.xlsx
+++ b/shabbatot/2026-10-30.xlsx
@@ -24,10 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -1537,7 +1536,7 @@
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>דבר תורה, עוגות, ושירה</t>
+          <t>דבר תורה, עוגות, ושירה · מעבירים: תמר</t>
         </is>
       </c>
       <c r="F19" s="49" t="n">

--- a/shabbatot/2026-10-30.xlsx
+++ b/shabbatot/2026-10-30.xlsx
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="F11" s="53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G11" s="31" t="inlineStr">
         <is>

--- a/shabbatot/2026-10-30.xlsx
+++ b/shabbatot/2026-10-30.xlsx
@@ -1450,7 +1450,11 @@
         </is>
       </c>
       <c r="D16" s="48" t="n"/>
-      <c r="E16" s="21" t="n"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>מעבירים: של״ו רובינשטיין</t>
+        </is>
+      </c>
       <c r="F16" s="49" t="n">
         <v>0.4895833333333333</v>
       </c>
@@ -2749,7 +2753,7 @@
       </c>
       <c r="G21" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, שי- לי וולגמוט</t>
+          <t>משה אוברשטיין, ארבל פרנקו</t>
         </is>
       </c>
       <c r="H21" s="48" t="n"/>
@@ -2790,7 +2794,7 @@
       </c>
       <c r="G22" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, שי- לי וולגמוט</t>
+          <t>משה אוברשטיין, ארבל פרנקו</t>
         </is>
       </c>
       <c r="H22" s="48" t="n"/>
@@ -2830,7 +2834,7 @@
       </c>
       <c r="G23" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, שי- לי וולגמוט</t>
+          <t>משה אוברשטיין, ארבל פרנקו</t>
         </is>
       </c>
       <c r="H23" s="48" t="n"/>
@@ -2870,7 +2874,7 @@
       </c>
       <c r="G24" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, שי- לי וולגמוט</t>
+          <t>משה אוברשטיין, ארבל פרנקו</t>
         </is>
       </c>
       <c r="H24" s="48" t="n"/>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="G25" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, שי- לי וולגמוט</t>
+          <t>משה אוברשטיין, ארבל פרנקו</t>
         </is>
       </c>
       <c r="H25" s="48" t="n"/>
@@ -3042,7 +3046,7 @@
       </c>
       <c r="G28" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, כליל בלאוקופף, רותם דרור, של״ו רובינשטיין, ארבל פרנקו, נבו בלוך, אוריה תעשה</t>
+          <t>הילי אלפסי, שי- לי וולגמוט, כליל בלאוקופף, רותם דרור, של״ו רובינשטיין, נבו בלוך, אוריה תעשה</t>
         </is>
       </c>
       <c r="H28" s="48" t="n"/>
@@ -3078,7 +3082,7 @@
       <c r="F29" s="53" t="n"/>
       <c r="G29" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, כליל בלאוקופף, רותם דרור, של״ו רובינשטיין, ארבל פרנקו, נבו בלוך, אוריה תעשה</t>
+          <t>הילי אלפסי, שי- לי וולגמוט, כליל בלאוקופף, רותם דרור, של״ו רובינשטיין, נבו בלוך, אוריה תעשה</t>
         </is>
       </c>
       <c r="H29" s="48" t="n"/>
@@ -3336,7 +3340,7 @@
       </c>
       <c r="G35" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, נועם ישראל קומפאס, הילי אלפסי, הילה עזרא, נגה שוהם</t>
+          <t>מעיין רחל דינר, נועם ישראל קומפאס, הילה עזרא, נגה שוהם, ניתאי שלום</t>
         </is>
       </c>
       <c r="H35" s="48" t="n"/>
@@ -3372,7 +3376,7 @@
       <c r="F36" s="53" t="n"/>
       <c r="G36" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, נועם ישראל קומפאס, הילי אלפסי, הילה עזרא, נגה שוהם</t>
+          <t>מעיין רחל דינר, נועם ישראל קומפאס, הילה עזרא, נגה שוהם, ניתאי שלום</t>
         </is>
       </c>
       <c r="H36" s="48" t="n"/>
@@ -4907,12 +4911,12 @@
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>ניתאי שלום</t>
+          <t>ארבל פרנקו</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, שי- לי וולגמוט</t>
+          <t>משה אוברשטיין, ארבל פרנקו</t>
         </is>
       </c>
       <c r="F13" s="50">
@@ -4978,7 +4982,7 @@
       </c>
       <c r="E15" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, כליל בלאוקופף, רותם דרור, של״ו רובינשטיין, ארבל פרנקו, נבו בלוך, אוריה תעשה</t>
+          <t>הילי אלפסי, שי- לי וולגמוט, כליל בלאוקופף, רותם דרור, של״ו רובינשטיין, נבו בלוך, אוריה תעשה</t>
         </is>
       </c>
       <c r="F15" s="50">
@@ -5110,7 +5114,7 @@
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, נועם ישראל קומפאס, הילי אלפסי, הילה עזרא, נגה שוהם</t>
+          <t>מעיין רחל דינר, נועם ישראל קומפאס, הילה עזרא, נגה שוהם, ניתאי שלום</t>
         </is>
       </c>
       <c r="F19" s="50">
@@ -5491,7 +5495,7 @@
       </c>
       <c r="E3" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; גסטרונומים</t>
+          <t>בית מדרש; פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F3" s="50">
@@ -5598,7 +5602,7 @@
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; פינוי ארוחת צהריים וסעודה שלישית</t>
+          <t>מטבוחה; פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="F6" s="50">
@@ -5886,7 +5890,7 @@
       </c>
       <c r="E14" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון חדר האוכל במוצ"ש</t>
+          <t>גסטרונומים; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F14" s="50">
@@ -7168,7 +7172,7 @@
       </c>
       <c r="E50" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; פינוי ארוחת ערב</t>
+          <t>בית מדרש; גסטרונומים</t>
         </is>
       </c>
       <c r="F50" s="50">
@@ -7349,7 +7353,7 @@
       </c>
       <c r="E55" s="34" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס; גסטרונומים</t>
+          <t>עוגיות שוקולד צ'יפס; פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="F55" s="50">
@@ -14524,7 +14528,7 @@
       </c>
       <c r="B241" s="59" t="inlineStr">
         <is>
-          <t>ניתאי שלום</t>
+          <t>ארבל פרנקו</t>
         </is>
       </c>
       <c r="C241" s="60" t="inlineStr">
@@ -14547,7 +14551,7 @@
       </c>
       <c r="B242" s="59" t="inlineStr">
         <is>
-          <t>שי- לי וולגמוט</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C242" s="60" t="inlineStr">
@@ -14662,7 +14666,7 @@
       </c>
       <c r="B247" s="59" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="C247" s="60" t="inlineStr">
@@ -14708,7 +14712,7 @@
       </c>
       <c r="B249" s="59" t="inlineStr">
         <is>
-          <t>משה אוברשטיין</t>
+          <t>נבו בלוך</t>
         </is>
       </c>
       <c r="C249" s="60" t="inlineStr">
@@ -14731,7 +14735,7 @@
       </c>
       <c r="B250" s="59" t="inlineStr">
         <is>
-          <t>נבו בלוך</t>
+          <t>רותם דרור</t>
         </is>
       </c>
       <c r="C250" s="60" t="inlineStr">
@@ -14754,7 +14758,7 @@
       </c>
       <c r="B251" s="59" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>שי- לי וולגמוט</t>
         </is>
       </c>
       <c r="C251" s="60" t="inlineStr">
@@ -14823,7 +14827,7 @@
       </c>
       <c r="B254" s="59" t="inlineStr">
         <is>
-          <t>הילי אלפסי</t>
+          <t>מעיין רחל דינר</t>
         </is>
       </c>
       <c r="C254" s="60" t="inlineStr">
@@ -14846,7 +14850,7 @@
       </c>
       <c r="B255" s="59" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר</t>
+          <t>נגה שוהם</t>
         </is>
       </c>
       <c r="C255" s="60" t="inlineStr">
@@ -14869,7 +14873,7 @@
       </c>
       <c r="B256" s="59" t="inlineStr">
         <is>
-          <t>נגה שוהם</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C256" s="60" t="inlineStr">
@@ -14892,7 +14896,7 @@
       </c>
       <c r="B257" s="59" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>ניתאי שלום</t>
         </is>
       </c>
       <c r="C257" s="60" t="inlineStr">

--- a/shabbatot/2026-10-30.xlsx
+++ b/shabbatot/2026-10-30.xlsx
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="C12" s="47" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="E12" s="21" t="n"/>
       <c r="F12" s="49">
-        <f>IF($B$4="","",MAX(TIME(19,0,0),ROUNDUP(ROUND(($B$4+TIME(1,45,0))*1440,0)/15,0)*15/1440))</f>
+        <f>IF($B$4="","",ROUNDUP(ROUND(($B$4+TIME(1,45,0))*1440,0)/15,0)*15/1440)</f>
         <v/>
       </c>
       <c r="G12" s="50">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="B13" s="46" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="C13" s="47" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="B14" s="46" t="n">
-        <v>0.90625</v>
+        <v>0.875</v>
       </c>
       <c r="C14" s="47" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="C23" s="55" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="D23" s="48" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="C26" s="55" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C27" s="55" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="D27" s="48" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="C28" s="55" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="D28" s="48" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="C30" s="55" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="D30" s="48" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="C31" s="55" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="D31" s="48" t="inlineStr">
         <is>
